--- a/Parts_list/HeadfixedSipper_parts.xlsx
+++ b/Parts_list/HeadfixedSipper_parts.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{584071C6-D758-4865-AFFF-6A5C62A1DBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexxai\Documents\GitHub\Head_fixed_wheel\Parts_list\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C1C2C5-7F7A-445E-8246-241D8D033A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="340" yWindow="400" windowWidth="27380" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="1" r:id="rId1"/>
@@ -34,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="189">
   <si>
     <t>REF</t>
   </si>
@@ -602,6 +607,24 @@
   <si>
     <t>4x to secure servos in slots</t>
   </si>
+  <si>
+    <t>1010-Black | 1.00” X 1.00” T-Slotted Profile - Four Open T-Slots</t>
+  </si>
+  <si>
+    <t>8" long, 1x1" 80/20 extruded aluminum rail</t>
+  </si>
+  <si>
+    <t>8 per setup</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Can be purchased through Workday from supplier "80-20 Inc"</t>
+  </si>
+  <si>
+    <t>1010-Black</t>
+  </si>
 </sst>
 </file>
 
@@ -610,7 +633,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00000000000000000000000000_);_(&quot;$&quot;* \(#,##0.00000000000000000000000000\);_(&quot;$&quot;* &quot;-&quot;??????????????????????????_);_(@_)"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -668,6 +691,13 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF555555"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -770,7 +800,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -802,6 +832,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1139,16 +1172,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H55"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="4" width="53.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" customWidth="1"/>
+    <col min="3" max="4" width="53.81640625" customWidth="1"/>
+    <col min="5" max="5" width="16.453125" customWidth="1"/>
     <col min="6" max="6" width="41" customWidth="1"/>
-    <col min="8" max="8" width="67.140625" customWidth="1"/>
+    <col min="8" max="8" width="67.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21">
+    <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1164,9 +1197,11 @@
       <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="F1" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>5</v>
       </c>
@@ -1176,24 +1211,27 @@
       <c r="E2" s="15"/>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>184</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>8</v>
+        <v>185</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>183</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="F3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
@@ -1211,7 +1249,7 @@
       </c>
       <c r="F4" s="3"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
@@ -1228,7 +1266,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>19</v>
       </c>
@@ -1245,7 +1283,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>23</v>
       </c>
@@ -1262,7 +1300,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>26</v>
       </c>
@@ -1279,7 +1317,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>31</v>
       </c>
@@ -1296,7 +1334,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>34</v>
       </c>
@@ -1313,7 +1351,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="15" t="s">
         <v>37</v>
       </c>
@@ -1322,7 +1360,7 @@
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
@@ -1339,7 +1377,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>42</v>
       </c>
@@ -1356,7 +1394,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>45</v>
       </c>
@@ -1373,7 +1411,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>48</v>
       </c>
@@ -1390,7 +1428,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="15" t="s">
         <v>52</v>
       </c>
@@ -1399,7 +1437,7 @@
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>53</v>
       </c>
@@ -1416,7 +1454,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>58</v>
       </c>
@@ -1433,7 +1471,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>63</v>
       </c>
@@ -1450,7 +1488,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>67</v>
       </c>
@@ -1467,7 +1505,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>70</v>
       </c>
@@ -1484,7 +1522,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>73</v>
       </c>
@@ -1501,7 +1539,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>76</v>
       </c>
@@ -1518,7 +1556,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>80</v>
       </c>
@@ -1535,7 +1573,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
         <v>83</v>
       </c>
@@ -1552,7 +1590,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
         <v>87</v>
       </c>
@@ -1569,7 +1607,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="15" t="s">
         <v>90</v>
       </c>
@@ -1578,7 +1616,7 @@
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
         <v>91</v>
       </c>
@@ -1595,7 +1633,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>95</v>
       </c>
@@ -1612,7 +1650,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
         <v>98</v>
       </c>
@@ -1629,7 +1667,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="16" t="s">
         <v>101</v>
       </c>
@@ -1638,7 +1676,7 @@
       <c r="D31" s="15"/>
       <c r="E31" s="15"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
         <v>102</v>
       </c>
@@ -1655,7 +1693,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
         <v>104</v>
       </c>
@@ -1672,7 +1710,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="15" t="s">
         <v>106</v>
       </c>
@@ -1681,7 +1719,7 @@
       <c r="D34" s="15"/>
       <c r="E34" s="15"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
         <v>107</v>
       </c>
@@ -1698,7 +1736,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
         <v>110</v>
       </c>
@@ -1715,7 +1753,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
         <v>113</v>
       </c>
@@ -1732,7 +1770,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="16" t="s">
         <v>116</v>
       </c>
@@ -1741,7 +1779,7 @@
       <c r="D38" s="15"/>
       <c r="E38" s="15"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
         <v>117</v>
       </c>
@@ -1758,7 +1796,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
         <v>120</v>
       </c>
@@ -1775,7 +1813,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
         <v>124</v>
       </c>
@@ -1792,7 +1830,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="15" t="s">
         <v>128</v>
       </c>
@@ -1801,7 +1839,7 @@
       <c r="D42" s="15"/>
       <c r="E42" s="15"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>129</v>
       </c>
@@ -1815,7 +1853,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>133</v>
       </c>
@@ -1829,7 +1867,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>137</v>
       </c>
@@ -1843,7 +1881,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>141</v>
       </c>
@@ -1857,7 +1895,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>144</v>
       </c>
@@ -1871,7 +1909,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>148</v>
       </c>
@@ -1885,7 +1923,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>152</v>
       </c>
@@ -1897,7 +1935,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="29.25">
+    <row r="50" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>155</v>
       </c>
@@ -1911,7 +1949,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="29.25">
+    <row r="51" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>159</v>
       </c>
@@ -1925,7 +1963,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>163</v>
       </c>
@@ -1939,7 +1977,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>167</v>
       </c>
@@ -1953,7 +1991,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>171</v>
       </c>
@@ -1967,7 +2005,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C55" s="13"/>
     </row>
   </sheetData>
@@ -1982,48 +2020,47 @@
     <mergeCell ref="A31:E31"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" display="Source" xr:uid="{4A1F82CA-B846-4A7F-BDD9-A7E0EF4975CC}"/>
-    <hyperlink ref="E3" r:id="rId2" display="Product ID:5451518Category:Metals &amp; Alloys" xr:uid="{08699B00-9267-4E65-B255-76D9D60A8E17}"/>
-    <hyperlink ref="D4" r:id="rId3" location="ad-image-0" xr:uid="{DEF11C8B-3DBF-41F1-B859-E9CE19AB688C}"/>
-    <hyperlink ref="E4" r:id="rId4" location="ad-image-0" xr:uid="{11F39A8C-5434-4233-96C7-030FF6A581A1}"/>
-    <hyperlink ref="D5" r:id="rId5" xr:uid="{16C9C90E-3F04-418F-BA95-9B062F18C717}"/>
-    <hyperlink ref="E5" r:id="rId6" xr:uid="{D728358E-0014-4286-8BB0-2CBE636436C8}"/>
-    <hyperlink ref="D6" r:id="rId7" xr:uid="{75D542E9-ACA5-468C-8643-FFD02F246ADB}"/>
-    <hyperlink ref="E6" r:id="rId8" xr:uid="{8455D848-F823-4C37-A3A2-0D47D7C3DAC7}"/>
-    <hyperlink ref="D7" r:id="rId9" xr:uid="{1F733267-18DF-4046-9717-AF75896CFA5D}"/>
-    <hyperlink ref="E7" r:id="rId10" xr:uid="{5341FE96-266B-4E3C-A23F-3DD44F2393E2}"/>
-    <hyperlink ref="D8" r:id="rId11" xr:uid="{C3F90499-9A86-4F62-A1D8-6C463C32C38B}"/>
-    <hyperlink ref="D9" r:id="rId12" xr:uid="{8F6634E7-AA45-491C-AE2F-885536673DBA}"/>
-    <hyperlink ref="E9" r:id="rId13" xr:uid="{BE48753A-D882-4F19-8D56-0E606EC00CF4}"/>
-    <hyperlink ref="D10" r:id="rId14" xr:uid="{EC65AAE4-5D5E-4CD9-B9A8-CE0F54D0240D}"/>
-    <hyperlink ref="E10" r:id="rId15" display="TRA75/M" xr:uid="{6EFC353C-18CC-4BD4-88DD-4B40827D77E5}"/>
-    <hyperlink ref="D10:E10" r:id="rId16" display="THOR" xr:uid="{F275E39F-B5B3-411F-8279-29DD1BFA07E0}"/>
-    <hyperlink ref="D44" r:id="rId17" xr:uid="{3B668A69-170E-4149-A428-376C4CDF867B}"/>
-    <hyperlink ref="D45" r:id="rId18" xr:uid="{4EA95586-8F44-4959-BD4B-B9EAC40668FD}"/>
-    <hyperlink ref="D46" r:id="rId19" xr:uid="{4BA77E4C-DF89-4426-9F23-4A6156C708A3}"/>
-    <hyperlink ref="D47" r:id="rId20" xr:uid="{1DDEFCE4-F32B-4BF4-A62C-5566066791F7}"/>
-    <hyperlink ref="D43" r:id="rId21" xr:uid="{D86B9ACB-622F-48E2-9C26-EC9730A2D6B5}"/>
-    <hyperlink ref="D48" r:id="rId22" xr:uid="{467CA380-5CD9-4D1A-A959-9B5A2F6C1941}"/>
-    <hyperlink ref="D49" r:id="rId23" display="https://www.amazon.com/Kadrick-Stainless-Screws-3mm-16mm-Lengths/dp/B0D962TJHX/ref=sr_1_1_sspa?crid=4MNJF0LWQ6TG&amp;dib=eyJ2IjoiMSJ9.gRSd3sL9p4ZOy5Wqs3KfhZDWsaFjMgTm71QBWqoMM7zKeUjEEwbtS03aMpoos_BgPZqB_Ja7acNwyde7DZANV6Y9zhoGCWHEmEoy9FJ5K62Az6y8AljukXz_yZDWwFlHbEtfnhUNycfAnCLaLPhixKZpkCm5J1_zQ3VJUj1_NyyRosaGDjMBrUiDnNV35xmBvVXjhm9Bhc6xqBzmsEOoiBIsKYiyJX83W2JhkGy6eZoLGHSMaFNxlEdlsVqoUm0b7gRDko7EbA2lQmH8CT66SdEdpPNTOKv0_Z5BwPjZaQ0.EHvLV7ct5_R-NSHPjhJDhnCD29dGGvnV74ToBfpXi_Y&amp;dib_tag=se&amp;keywords=m4+set+screw&amp;qid=1737936533&amp;s=hi&amp;sprefix=m4+set+scre%2Ctools%2C114&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1" xr:uid="{E643B20E-8F07-4335-9733-91C6781711E7}"/>
-    <hyperlink ref="D12:E12" r:id="rId24" display="Amazon" xr:uid="{8A0B497D-5166-4A6C-9EEC-976AF2ABFB09}"/>
-    <hyperlink ref="D13:E13" r:id="rId25" display="Amazon" xr:uid="{03B0ACEC-1384-48AD-B267-19C6274FB23F}"/>
-    <hyperlink ref="D14:E14" r:id="rId26" display="Amazon" xr:uid="{E524F7C5-C01B-4728-B394-92202FC3AA66}"/>
-    <hyperlink ref="D15:E15" r:id="rId27" display="Adafruit I2C Stemma QT" xr:uid="{85EF1A27-EEA2-4685-9496-9E3ECD888FEA}"/>
-    <hyperlink ref="D17:E17" r:id="rId28" display="Ebay" xr:uid="{9B459267-111B-41A9-ADAD-9BB2E546E802}"/>
-    <hyperlink ref="D18:E18" r:id="rId29" location="part-numbers-specifications" display="The Lee Co" xr:uid="{56B71E26-18F4-48AF-B225-6976EF59FF5E}"/>
-    <hyperlink ref="D19:E19" r:id="rId30" display="Amazon" xr:uid="{67DC6BE1-5BE8-478B-9EA2-F9D5D712C3FF}"/>
-    <hyperlink ref="D20:E20" r:id="rId31" display="Amazon" xr:uid="{98A641E9-3EE3-44DD-8DE4-C0F76550347D}"/>
-    <hyperlink ref="D21:E21" r:id="rId32" display="Amazon" xr:uid="{FF134FC5-E51A-4B66-8CA2-41C6F261F8B4}"/>
-    <hyperlink ref="D22:E22" r:id="rId33" display="Amazon, best I can find" xr:uid="{F0B7A50A-5053-47F0-861E-0000996262A7}"/>
-    <hyperlink ref="D23:E23" r:id="rId34" display="DigiKey" xr:uid="{647F1A7A-5059-41BA-8D70-C3D4B03D2D08}"/>
-    <hyperlink ref="D24:E24" r:id="rId35" display="Amazon" xr:uid="{DEECCD50-2092-4905-A5CB-BB6A5B4CFB17}"/>
-    <hyperlink ref="D26:E26" r:id="rId36" display="Amazon" xr:uid="{B06D8FC3-BC09-4C1B-9A6F-A98462565E1C}"/>
-    <hyperlink ref="D25:E25" r:id="rId37" display="Amazon, best I can find" xr:uid="{15502A57-572E-48C6-85E6-4B15AEEF9801}"/>
-    <hyperlink ref="D50" r:id="rId38" xr:uid="{640F538B-F70D-4AF9-BD6E-654502731B19}"/>
-    <hyperlink ref="D51" r:id="rId39" xr:uid="{5A481454-E1C6-40B6-ABAD-FA19FE498D62}"/>
-    <hyperlink ref="D52" r:id="rId40" xr:uid="{3B1B2211-EA81-471E-BF4B-687E0FCE54A9}"/>
-    <hyperlink ref="D53" r:id="rId41" xr:uid="{E819B334-06D2-4DCB-8E6F-44F7AE7A486A}"/>
-    <hyperlink ref="D54" r:id="rId42" xr:uid="{FDD23193-A8EC-4DE2-A415-344324EA2176}"/>
+    <hyperlink ref="D4" r:id="rId1" location="ad-image-0" xr:uid="{DEF11C8B-3DBF-41F1-B859-E9CE19AB688C}"/>
+    <hyperlink ref="E4" r:id="rId2" location="ad-image-0" xr:uid="{11F39A8C-5434-4233-96C7-030FF6A581A1}"/>
+    <hyperlink ref="D5" r:id="rId3" xr:uid="{16C9C90E-3F04-418F-BA95-9B062F18C717}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{D728358E-0014-4286-8BB0-2CBE636436C8}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{75D542E9-ACA5-468C-8643-FFD02F246ADB}"/>
+    <hyperlink ref="E6" r:id="rId6" xr:uid="{8455D848-F823-4C37-A3A2-0D47D7C3DAC7}"/>
+    <hyperlink ref="D7" r:id="rId7" xr:uid="{1F733267-18DF-4046-9717-AF75896CFA5D}"/>
+    <hyperlink ref="E7" r:id="rId8" xr:uid="{5341FE96-266B-4E3C-A23F-3DD44F2393E2}"/>
+    <hyperlink ref="D8" r:id="rId9" xr:uid="{C3F90499-9A86-4F62-A1D8-6C463C32C38B}"/>
+    <hyperlink ref="D9" r:id="rId10" xr:uid="{8F6634E7-AA45-491C-AE2F-885536673DBA}"/>
+    <hyperlink ref="E9" r:id="rId11" xr:uid="{BE48753A-D882-4F19-8D56-0E606EC00CF4}"/>
+    <hyperlink ref="D10" r:id="rId12" xr:uid="{EC65AAE4-5D5E-4CD9-B9A8-CE0F54D0240D}"/>
+    <hyperlink ref="E10" r:id="rId13" display="TRA75/M" xr:uid="{6EFC353C-18CC-4BD4-88DD-4B40827D77E5}"/>
+    <hyperlink ref="D10:E10" r:id="rId14" display="THOR" xr:uid="{F275E39F-B5B3-411F-8279-29DD1BFA07E0}"/>
+    <hyperlink ref="D44" r:id="rId15" xr:uid="{3B668A69-170E-4149-A428-376C4CDF867B}"/>
+    <hyperlink ref="D45" r:id="rId16" xr:uid="{4EA95586-8F44-4959-BD4B-B9EAC40668FD}"/>
+    <hyperlink ref="D46" r:id="rId17" xr:uid="{4BA77E4C-DF89-4426-9F23-4A6156C708A3}"/>
+    <hyperlink ref="D47" r:id="rId18" xr:uid="{1DDEFCE4-F32B-4BF4-A62C-5566066791F7}"/>
+    <hyperlink ref="D43" r:id="rId19" xr:uid="{D86B9ACB-622F-48E2-9C26-EC9730A2D6B5}"/>
+    <hyperlink ref="D48" r:id="rId20" xr:uid="{467CA380-5CD9-4D1A-A959-9B5A2F6C1941}"/>
+    <hyperlink ref="D49" r:id="rId21" display="https://www.amazon.com/Kadrick-Stainless-Screws-3mm-16mm-Lengths/dp/B0D962TJHX/ref=sr_1_1_sspa?crid=4MNJF0LWQ6TG&amp;dib=eyJ2IjoiMSJ9.gRSd3sL9p4ZOy5Wqs3KfhZDWsaFjMgTm71QBWqoMM7zKeUjEEwbtS03aMpoos_BgPZqB_Ja7acNwyde7DZANV6Y9zhoGCWHEmEoy9FJ5K62Az6y8AljukXz_yZDWwFlHbEtfnhUNycfAnCLaLPhixKZpkCm5J1_zQ3VJUj1_NyyRosaGDjMBrUiDnNV35xmBvVXjhm9Bhc6xqBzmsEOoiBIsKYiyJX83W2JhkGy6eZoLGHSMaFNxlEdlsVqoUm0b7gRDko7EbA2lQmH8CT66SdEdpPNTOKv0_Z5BwPjZaQ0.EHvLV7ct5_R-NSHPjhJDhnCD29dGGvnV74ToBfpXi_Y&amp;dib_tag=se&amp;keywords=m4+set+screw&amp;qid=1737936533&amp;s=hi&amp;sprefix=m4+set+scre%2Ctools%2C114&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1" xr:uid="{E643B20E-8F07-4335-9733-91C6781711E7}"/>
+    <hyperlink ref="D12:E12" r:id="rId22" display="Amazon" xr:uid="{8A0B497D-5166-4A6C-9EEC-976AF2ABFB09}"/>
+    <hyperlink ref="D13:E13" r:id="rId23" display="Amazon" xr:uid="{03B0ACEC-1384-48AD-B267-19C6274FB23F}"/>
+    <hyperlink ref="D14:E14" r:id="rId24" display="Amazon" xr:uid="{E524F7C5-C01B-4728-B394-92202FC3AA66}"/>
+    <hyperlink ref="D15:E15" r:id="rId25" display="Adafruit I2C Stemma QT" xr:uid="{85EF1A27-EEA2-4685-9496-9E3ECD888FEA}"/>
+    <hyperlink ref="D17:E17" r:id="rId26" display="Ebay" xr:uid="{9B459267-111B-41A9-ADAD-9BB2E546E802}"/>
+    <hyperlink ref="D18:E18" r:id="rId27" location="part-numbers-specifications" display="The Lee Co" xr:uid="{56B71E26-18F4-48AF-B225-6976EF59FF5E}"/>
+    <hyperlink ref="D19:E19" r:id="rId28" display="Amazon" xr:uid="{67DC6BE1-5BE8-478B-9EA2-F9D5D712C3FF}"/>
+    <hyperlink ref="D20:E20" r:id="rId29" display="Amazon" xr:uid="{98A641E9-3EE3-44DD-8DE4-C0F76550347D}"/>
+    <hyperlink ref="D21:E21" r:id="rId30" display="Amazon" xr:uid="{FF134FC5-E51A-4B66-8CA2-41C6F261F8B4}"/>
+    <hyperlink ref="D22:E22" r:id="rId31" display="Amazon, best I can find" xr:uid="{F0B7A50A-5053-47F0-861E-0000996262A7}"/>
+    <hyperlink ref="D23:E23" r:id="rId32" display="DigiKey" xr:uid="{647F1A7A-5059-41BA-8D70-C3D4B03D2D08}"/>
+    <hyperlink ref="D24:E24" r:id="rId33" display="Amazon" xr:uid="{DEECCD50-2092-4905-A5CB-BB6A5B4CFB17}"/>
+    <hyperlink ref="D26:E26" r:id="rId34" display="Amazon" xr:uid="{B06D8FC3-BC09-4C1B-9A6F-A98462565E1C}"/>
+    <hyperlink ref="D25:E25" r:id="rId35" display="Amazon, best I can find" xr:uid="{15502A57-572E-48C6-85E6-4B15AEEF9801}"/>
+    <hyperlink ref="D50" r:id="rId36" xr:uid="{640F538B-F70D-4AF9-BD6E-654502731B19}"/>
+    <hyperlink ref="D51" r:id="rId37" xr:uid="{5A481454-E1C6-40B6-ABAD-FA19FE498D62}"/>
+    <hyperlink ref="D52" r:id="rId38" xr:uid="{3B1B2211-EA81-471E-BF4B-687E0FCE54A9}"/>
+    <hyperlink ref="D53" r:id="rId39" xr:uid="{E819B334-06D2-4DCB-8E6F-44F7AE7A486A}"/>
+    <hyperlink ref="D54" r:id="rId40" xr:uid="{FDD23193-A8EC-4DE2-A415-344324EA2176}"/>
+    <hyperlink ref="D3" r:id="rId41" display="https://8020.net/1010-black.html" xr:uid="{6D315072-03C5-4CCB-8E05-7B856BD1B10E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2032,15 +2069,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4217DB71-145D-439F-ADA4-6ACCE49B79C3}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="48.140625" customWidth="1"/>
-    <col min="3" max="3" width="64.140625" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="2" max="2" width="48.1796875" customWidth="1"/>
+    <col min="3" max="3" width="64.1796875" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2057,7 +2094,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -2074,7 +2111,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
@@ -2091,7 +2128,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>15</v>
       </c>
@@ -2108,7 +2145,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>19</v>
       </c>
@@ -2125,7 +2162,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>23</v>
       </c>
@@ -2142,7 +2179,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>26</v>
       </c>
@@ -2159,7 +2196,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>31</v>
       </c>
@@ -2176,7 +2213,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>34</v>
       </c>
@@ -2193,7 +2230,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="16" t="s">
         <v>175</v>
       </c>
@@ -2202,7 +2239,7 @@
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>117</v>
       </c>
@@ -2219,7 +2256,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>120</v>
       </c>
@@ -2236,7 +2273,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>124</v>
       </c>
@@ -2253,7 +2290,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="18.75" customHeight="1">
+    <row r="15" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
         <v>128</v>
       </c>
@@ -2262,7 +2299,7 @@
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>129</v>
       </c>
@@ -2276,7 +2313,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>133</v>
       </c>
@@ -2290,7 +2327,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>137</v>
       </c>
@@ -2304,7 +2341,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>141</v>
       </c>
@@ -2318,7 +2355,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>144</v>
       </c>
@@ -2332,7 +2369,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>148</v>
       </c>
@@ -2346,7 +2383,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>152</v>
       </c>
@@ -2394,16 +2431,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DD83E9E-D72C-4821-A595-BB29CDD6856C}">
   <dimension ref="A1:E284"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" customWidth="1"/>
-    <col min="3" max="3" width="43.7109375" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="23.54296875" customWidth="1"/>
+    <col min="3" max="3" width="43.7265625" customWidth="1"/>
+    <col min="4" max="4" width="24.54296875" customWidth="1"/>
+    <col min="5" max="5" width="12.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2420,7 +2457,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>38</v>
       </c>
@@ -2437,7 +2474,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>42</v>
       </c>
@@ -2454,7 +2491,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>45</v>
       </c>
@@ -2471,7 +2508,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>48</v>
       </c>
@@ -2488,7 +2525,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>91</v>
       </c>
@@ -2505,7 +2542,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>95</v>
       </c>
@@ -2522,7 +2559,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>98</v>
       </c>
@@ -2539,7 +2576,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="16" t="s">
         <v>177</v>
       </c>
@@ -2547,7 +2584,7 @@
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>102</v>
       </c>
@@ -2564,7 +2601,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>104</v>
       </c>
@@ -2581,7 +2618,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="17" t="s">
         <v>128</v>
       </c>
@@ -2589,7 +2626,7 @@
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
     </row>
-    <row r="13" spans="1:5" ht="33.75" customHeight="1">
+    <row r="13" spans="1:5" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>133</v>
       </c>
@@ -2603,7 +2640,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>152</v>
       </c>
@@ -2617,7 +2654,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="29.25">
+    <row r="15" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>155</v>
       </c>
@@ -2631,7 +2668,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="29.25">
+    <row r="16" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>159</v>
       </c>
@@ -2645,7 +2682,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>163</v>
       </c>
@@ -2659,805 +2696,805 @@
         <v>166</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18"/>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19"/>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20"/>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21"/>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22"/>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23"/>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24"/>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25"/>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26"/>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30"/>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34"/>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35"/>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36"/>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37"/>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38"/>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39"/>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40"/>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42"/>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43"/>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45"/>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46"/>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47"/>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48"/>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49"/>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50"/>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51"/>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52"/>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53"/>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54"/>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57"/>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58"/>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59"/>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60"/>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61"/>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63"/>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64"/>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65"/>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66"/>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67"/>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68"/>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69"/>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70"/>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71"/>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72"/>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73"/>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74"/>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75"/>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76"/>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77"/>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81"/>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82"/>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83"/>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A84"/>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A85"/>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86"/>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87"/>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89"/>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90"/>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91"/>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92"/>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93"/>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94"/>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95"/>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96"/>
     </row>
-    <row r="97" spans="1:1">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97"/>
     </row>
-    <row r="98" spans="1:1">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99"/>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100"/>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101"/>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A102"/>
     </row>
-    <row r="103" spans="1:1">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A103"/>
     </row>
-    <row r="104" spans="1:1">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:1">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A105"/>
     </row>
-    <row r="106" spans="1:1">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A106"/>
     </row>
-    <row r="107" spans="1:1">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A107"/>
     </row>
-    <row r="108" spans="1:1">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:1">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A109"/>
     </row>
-    <row r="110" spans="1:1">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A110"/>
     </row>
-    <row r="111" spans="1:1">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A111"/>
     </row>
-    <row r="112" spans="1:1">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A112"/>
     </row>
-    <row r="113" spans="1:1">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:1">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:1">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A115"/>
     </row>
-    <row r="116" spans="1:1">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A116"/>
     </row>
-    <row r="117" spans="1:1">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A117"/>
     </row>
-    <row r="118" spans="1:1">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A118"/>
     </row>
-    <row r="119" spans="1:1">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A119"/>
     </row>
-    <row r="120" spans="1:1">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A120"/>
     </row>
-    <row r="121" spans="1:1">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A121"/>
     </row>
-    <row r="122" spans="1:1">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A122"/>
     </row>
-    <row r="123" spans="1:1">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:1">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A124"/>
     </row>
-    <row r="125" spans="1:1">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A125"/>
     </row>
-    <row r="126" spans="1:1">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:1">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A127"/>
     </row>
-    <row r="128" spans="1:1">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A128"/>
     </row>
-    <row r="129" spans="1:1">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A129"/>
     </row>
-    <row r="130" spans="1:1">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:1">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:1">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A132"/>
     </row>
-    <row r="133" spans="1:1">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A133"/>
     </row>
-    <row r="134" spans="1:1">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A134"/>
     </row>
-    <row r="135" spans="1:1">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A135"/>
     </row>
-    <row r="136" spans="1:1">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A136"/>
     </row>
-    <row r="137" spans="1:1">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:1">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A138"/>
     </row>
-    <row r="139" spans="1:1">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A139"/>
     </row>
-    <row r="140" spans="1:1">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A140"/>
     </row>
-    <row r="141" spans="1:1">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A141"/>
     </row>
-    <row r="142" spans="1:1">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A142"/>
     </row>
-    <row r="143" spans="1:1">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A143"/>
     </row>
-    <row r="144" spans="1:1">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A144"/>
     </row>
-    <row r="145" spans="1:1">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A145"/>
     </row>
-    <row r="146" spans="1:1">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A146"/>
     </row>
-    <row r="147" spans="1:1">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A147"/>
     </row>
-    <row r="148" spans="1:1">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A148"/>
     </row>
-    <row r="149" spans="1:1">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A149"/>
     </row>
-    <row r="150" spans="1:1">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A150"/>
     </row>
-    <row r="151" spans="1:1">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A151"/>
     </row>
-    <row r="152" spans="1:1">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A152"/>
     </row>
-    <row r="153" spans="1:1">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A153"/>
     </row>
-    <row r="154" spans="1:1">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A154"/>
     </row>
-    <row r="155" spans="1:1">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A155"/>
     </row>
-    <row r="156" spans="1:1">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A156"/>
     </row>
-    <row r="157" spans="1:1">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A157"/>
     </row>
-    <row r="158" spans="1:1">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A158"/>
     </row>
-    <row r="159" spans="1:1">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:1">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A160"/>
     </row>
-    <row r="161" spans="1:1">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A161"/>
     </row>
-    <row r="162" spans="1:1">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A162"/>
     </row>
-    <row r="163" spans="1:1">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A163"/>
     </row>
-    <row r="164" spans="1:1">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A164"/>
     </row>
-    <row r="165" spans="1:1">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A165"/>
     </row>
-    <row r="166" spans="1:1">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A166"/>
     </row>
-    <row r="167" spans="1:1">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A167"/>
     </row>
-    <row r="168" spans="1:1">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A168"/>
     </row>
-    <row r="169" spans="1:1">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A169"/>
     </row>
-    <row r="170" spans="1:1">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A170"/>
     </row>
-    <row r="171" spans="1:1">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A171"/>
     </row>
-    <row r="172" spans="1:1">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A172"/>
     </row>
-    <row r="173" spans="1:1">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A173"/>
     </row>
-    <row r="174" spans="1:1">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A174"/>
     </row>
-    <row r="175" spans="1:1">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A175"/>
     </row>
-    <row r="176" spans="1:1">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A176"/>
     </row>
-    <row r="177" spans="1:1">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A177"/>
     </row>
-    <row r="178" spans="1:1">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A178"/>
     </row>
-    <row r="179" spans="1:1">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A179"/>
     </row>
-    <row r="180" spans="1:1">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A180"/>
     </row>
-    <row r="181" spans="1:1">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A181"/>
     </row>
-    <row r="182" spans="1:1">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A182"/>
     </row>
-    <row r="183" spans="1:1">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A183"/>
     </row>
-    <row r="184" spans="1:1">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A184"/>
     </row>
-    <row r="185" spans="1:1">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A185"/>
     </row>
-    <row r="186" spans="1:1">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A186"/>
     </row>
-    <row r="187" spans="1:1">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A187"/>
     </row>
-    <row r="188" spans="1:1">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A188"/>
     </row>
-    <row r="189" spans="1:1">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A189"/>
     </row>
-    <row r="190" spans="1:1">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A190"/>
     </row>
-    <row r="191" spans="1:1">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A191"/>
     </row>
-    <row r="192" spans="1:1">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A192"/>
     </row>
-    <row r="193" spans="1:1">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A193"/>
     </row>
-    <row r="194" spans="1:1">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A194"/>
     </row>
-    <row r="195" spans="1:1">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A195"/>
     </row>
-    <row r="196" spans="1:1">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A196"/>
     </row>
-    <row r="197" spans="1:1">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A197"/>
     </row>
-    <row r="198" spans="1:1">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A198"/>
     </row>
-    <row r="199" spans="1:1">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A199"/>
     </row>
-    <row r="200" spans="1:1">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A200"/>
     </row>
-    <row r="201" spans="1:1">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A201"/>
     </row>
-    <row r="202" spans="1:1">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A202"/>
     </row>
-    <row r="203" spans="1:1">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A203"/>
     </row>
-    <row r="204" spans="1:1">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A204"/>
     </row>
-    <row r="205" spans="1:1">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A205"/>
     </row>
-    <row r="206" spans="1:1">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A206"/>
     </row>
-    <row r="207" spans="1:1">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A207"/>
     </row>
-    <row r="208" spans="1:1">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A208"/>
     </row>
-    <row r="209" spans="1:1">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A209"/>
     </row>
-    <row r="210" spans="1:1">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A210"/>
     </row>
-    <row r="211" spans="1:1">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A211"/>
     </row>
-    <row r="212" spans="1:1">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A212"/>
     </row>
-    <row r="213" spans="1:1">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A213"/>
     </row>
-    <row r="214" spans="1:1">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A214"/>
     </row>
-    <row r="215" spans="1:1">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A215"/>
     </row>
-    <row r="216" spans="1:1">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A216"/>
     </row>
-    <row r="217" spans="1:1">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A217"/>
     </row>
-    <row r="218" spans="1:1">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A218"/>
     </row>
-    <row r="219" spans="1:1">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A219"/>
     </row>
-    <row r="220" spans="1:1">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A220"/>
     </row>
-    <row r="221" spans="1:1">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A221"/>
     </row>
-    <row r="222" spans="1:1">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A222"/>
     </row>
-    <row r="223" spans="1:1">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A223"/>
     </row>
-    <row r="224" spans="1:1">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A224"/>
     </row>
-    <row r="225" spans="1:1">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A225"/>
     </row>
-    <row r="226" spans="1:1">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A226"/>
     </row>
-    <row r="227" spans="1:1">
+    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A227"/>
     </row>
-    <row r="228" spans="1:1">
+    <row r="228" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A228"/>
     </row>
-    <row r="229" spans="1:1">
+    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A229"/>
     </row>
-    <row r="230" spans="1:1">
+    <row r="230" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A230"/>
     </row>
-    <row r="231" spans="1:1">
+    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A231"/>
     </row>
-    <row r="232" spans="1:1">
+    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A232"/>
     </row>
-    <row r="233" spans="1:1">
+    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A233"/>
     </row>
-    <row r="234" spans="1:1">
+    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A234"/>
     </row>
-    <row r="235" spans="1:1">
+    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A235"/>
     </row>
-    <row r="236" spans="1:1">
+    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A236"/>
     </row>
-    <row r="237" spans="1:1">
+    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A237"/>
     </row>
-    <row r="238" spans="1:1">
+    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A238"/>
     </row>
-    <row r="239" spans="1:1">
+    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A239"/>
     </row>
-    <row r="240" spans="1:1">
+    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A240"/>
     </row>
-    <row r="241" spans="1:1">
+    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A241"/>
     </row>
-    <row r="242" spans="1:1">
+    <row r="242" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A242"/>
     </row>
-    <row r="243" spans="1:1">
+    <row r="243" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A243"/>
     </row>
-    <row r="244" spans="1:1">
+    <row r="244" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A244"/>
     </row>
-    <row r="245" spans="1:1">
+    <row r="245" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A245"/>
     </row>
-    <row r="246" spans="1:1">
+    <row r="246" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A246"/>
     </row>
-    <row r="247" spans="1:1">
+    <row r="247" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A247"/>
     </row>
-    <row r="248" spans="1:1">
+    <row r="248" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A248"/>
     </row>
-    <row r="249" spans="1:1">
+    <row r="249" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A249"/>
     </row>
-    <row r="250" spans="1:1">
+    <row r="250" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A250"/>
     </row>
-    <row r="251" spans="1:1">
+    <row r="251" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A251"/>
     </row>
-    <row r="252" spans="1:1">
+    <row r="252" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A252"/>
     </row>
-    <row r="253" spans="1:1">
+    <row r="253" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A253"/>
     </row>
-    <row r="254" spans="1:1">
+    <row r="254" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A254"/>
     </row>
-    <row r="255" spans="1:1">
+    <row r="255" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A255"/>
     </row>
-    <row r="256" spans="1:1">
+    <row r="256" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A256"/>
     </row>
-    <row r="257" spans="1:1">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A257"/>
     </row>
-    <row r="258" spans="1:1">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A258"/>
     </row>
-    <row r="259" spans="1:1">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A259"/>
     </row>
-    <row r="260" spans="1:1">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A260"/>
     </row>
-    <row r="261" spans="1:1">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A261"/>
     </row>
-    <row r="262" spans="1:1">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A262"/>
     </row>
-    <row r="263" spans="1:1">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A263"/>
     </row>
-    <row r="264" spans="1:1">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A264"/>
     </row>
-    <row r="265" spans="1:1">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A265"/>
     </row>
-    <row r="266" spans="1:1">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A266"/>
     </row>
-    <row r="267" spans="1:1">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A267"/>
     </row>
-    <row r="268" spans="1:1">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A268"/>
     </row>
-    <row r="269" spans="1:1">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A269"/>
     </row>
-    <row r="270" spans="1:1">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A270"/>
     </row>
-    <row r="271" spans="1:1">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A271"/>
     </row>
-    <row r="272" spans="1:1">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A272"/>
     </row>
-    <row r="273" spans="1:1">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A273"/>
     </row>
-    <row r="274" spans="1:1">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A274"/>
     </row>
-    <row r="275" spans="1:1">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A275"/>
     </row>
-    <row r="276" spans="1:1">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A276"/>
     </row>
-    <row r="277" spans="1:1">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A277"/>
     </row>
-    <row r="278" spans="1:1">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A278"/>
     </row>
-    <row r="279" spans="1:1">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A279"/>
     </row>
-    <row r="280" spans="1:1">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A280"/>
     </row>
-    <row r="281" spans="1:1">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A281"/>
     </row>
-    <row r="282" spans="1:1">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A282"/>
     </row>
-    <row r="283" spans="1:1">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A283"/>
     </row>
-    <row r="284" spans="1:1">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A284" s="6"/>
     </row>
   </sheetData>
@@ -3483,15 +3520,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8D0AEA-6B1E-4A41-9706-8AEF427A5313}">
   <dimension ref="A1:XFD19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="39.28515625" customWidth="1"/>
-    <col min="3" max="3" width="64.85546875" customWidth="1"/>
-    <col min="4" max="4" width="20.42578125" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="39.26953125" customWidth="1"/>
+    <col min="3" max="3" width="64.81640625" customWidth="1"/>
+    <col min="4" max="4" width="20.453125" customWidth="1"/>
+    <col min="5" max="5" width="21.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" ht="21">
+    <row r="1" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3508,7 +3545,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384">
+    <row r="2" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
         <v>53</v>
       </c>
@@ -3525,7 +3562,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384">
+    <row r="3" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>58</v>
       </c>
@@ -3542,7 +3579,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384">
+    <row r="4" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>63</v>
       </c>
@@ -3559,7 +3596,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384">
+    <row r="5" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>67</v>
       </c>
@@ -3576,7 +3613,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384">
+    <row r="6" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>70</v>
       </c>
@@ -3593,7 +3630,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" customFormat="1">
+    <row r="7" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>73</v>
       </c>
@@ -3610,7 +3647,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" customFormat="1">
+    <row r="8" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>76</v>
       </c>
@@ -3627,7 +3664,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" customFormat="1">
+    <row r="9" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>80</v>
       </c>
@@ -3644,7 +3681,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" customFormat="1">
+    <row r="10" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>83</v>
       </c>
@@ -3661,7 +3698,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" customFormat="1">
+    <row r="11" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>87</v>
       </c>
@@ -3678,7 +3715,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" customFormat="1">
+    <row r="12" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>107</v>
       </c>
@@ -3695,7 +3732,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" customFormat="1">
+    <row r="13" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>110</v>
       </c>
@@ -3712,7 +3749,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" customFormat="1">
+    <row r="14" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>113</v>
       </c>
@@ -3729,7 +3766,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" customFormat="1">
+    <row r="15" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
         <v>128</v>
       </c>
@@ -3738,7 +3775,7 @@
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
     </row>
-    <row r="16" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" customFormat="1">
+    <row r="16" spans="1:1024 1028:2048 2052:3072 3076:4096 4100:5120 5124:6144 6148:7168 7172:8192 8196:9216 9220:10240 10244:11264 11268:12288 12292:13312 13316:14336 14340:15360 15364:16384" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>163</v>
       </c>
@@ -7847,7 +7884,7 @@
       <c r="XEZ16" s="3"/>
       <c r="XFD16" s="3"/>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>167</v>
       </c>
@@ -7861,7 +7898,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>171</v>
       </c>
@@ -7875,7 +7912,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="D19" s="3"/>
     </row>
   </sheetData>
